--- a/backend/wp_templates/D/D1 应收票据.xlsx
+++ b/backend/wp_templates/D/D1 应收票据.xlsx
@@ -5683,7 +5683,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="764">
+  <cellXfs count="765">
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0">
       <protection locked="0"/>
     </xf>
@@ -8358,6 +8358,10 @@
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -10282,7 +10286,7 @@
       <c r="K13" s="286"/>
       <c r="L13" s="286"/>
       <c r="M13" s="286"/>
-      <c r="N13" s="96"/>
+      <c r="N13" s="764"/>
       <c r="O13" s="286"/>
       <c r="P13" s="286"/>
       <c r="Q13" s="285">
@@ -10340,7 +10344,7 @@
       <c r="K14" s="286"/>
       <c r="L14" s="286"/>
       <c r="M14" s="286"/>
-      <c r="N14" s="96"/>
+      <c r="N14" s="764"/>
       <c r="O14" s="286"/>
       <c r="P14" s="286"/>
       <c r="Q14" s="285">
@@ -10398,7 +10402,7 @@
       <c r="K15" s="286"/>
       <c r="L15" s="286"/>
       <c r="M15" s="286"/>
-      <c r="N15" s="96"/>
+      <c r="N15" s="764"/>
       <c r="O15" s="286"/>
       <c r="P15" s="286"/>
       <c r="Q15" s="285">
@@ -10456,7 +10460,7 @@
       <c r="K16" s="286"/>
       <c r="L16" s="286"/>
       <c r="M16" s="286"/>
-      <c r="N16" s="96"/>
+      <c r="N16" s="764"/>
       <c r="O16" s="286"/>
       <c r="P16" s="286"/>
       <c r="Q16" s="285">
@@ -10512,7 +10516,7 @@
       <c r="K17" s="286"/>
       <c r="L17" s="286"/>
       <c r="M17" s="286"/>
-      <c r="N17" s="96"/>
+      <c r="N17" s="764"/>
       <c r="O17" s="286"/>
       <c r="P17" s="286"/>
       <c r="Q17" s="285">
@@ -10622,7 +10626,7 @@
       <c r="K19" s="286"/>
       <c r="L19" s="286"/>
       <c r="M19" s="286"/>
-      <c r="N19" s="96"/>
+      <c r="N19" s="764"/>
       <c r="O19" s="286"/>
       <c r="P19" s="286"/>
       <c r="Q19" s="285">
@@ -10680,7 +10684,7 @@
       <c r="K20" s="286"/>
       <c r="L20" s="286"/>
       <c r="M20" s="286"/>
-      <c r="N20" s="96"/>
+      <c r="N20" s="764"/>
       <c r="O20" s="286"/>
       <c r="P20" s="286"/>
       <c r="Q20" s="285">
@@ -10738,7 +10742,7 @@
       <c r="K21" s="286"/>
       <c r="L21" s="286"/>
       <c r="M21" s="286"/>
-      <c r="N21" s="96"/>
+      <c r="N21" s="764"/>
       <c r="O21" s="286"/>
       <c r="P21" s="286"/>
       <c r="Q21" s="285">
@@ -10796,7 +10800,7 @@
       <c r="K22" s="286"/>
       <c r="L22" s="286"/>
       <c r="M22" s="286"/>
-      <c r="N22" s="96"/>
+      <c r="N22" s="764"/>
       <c r="O22" s="286"/>
       <c r="P22" s="286"/>
       <c r="Q22" s="285">
@@ -10849,7 +10853,7 @@
       <c r="K23" s="286"/>
       <c r="L23" s="286"/>
       <c r="M23" s="286"/>
-      <c r="N23" s="96"/>
+      <c r="N23" s="764"/>
       <c r="O23" s="286"/>
       <c r="P23" s="286"/>
       <c r="Q23" s="285">

--- a/backend/wp_templates/D/D1 应收票据.xlsx
+++ b/backend/wp_templates/D/D1 应收票据.xlsx
@@ -10857,7 +10857,7 @@
       <c r="O23" s="286"/>
       <c r="P23" s="286"/>
       <c r="Q23" s="285">
-        <f t="shared" ref="Q23" si="1">IF(YEAR(A23)=YEAR($B$10)-1,H23,0)</f>
+        <f t="shared" ref="Q23" si="1">IF(YEAR(C23)=YEAR($B$10)-1,H23,0)</f>
         <v>0</v>
       </c>
       <c r="R23" s="285">

--- a/backend/wp_templates/D/D1 应收票据.xlsx
+++ b/backend/wp_templates/D/D1 应收票据.xlsx
@@ -16071,8 +16071,10 @@
       <c r="D13" s="18" t="s">
         <v>548</v>
       </c>
-      <c r="E13" s="18" t="s">
-        <v>549</v>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
       </c>
       <c r="F13" s="18" t="s">
         <v>550</v>
@@ -16088,10 +16090,7 @@
         <f>B14*C14</f>
         <v>0</v>
       </c>
-      <c r="E14" s="23">
-        <f>B14-D14</f>
-        <v>0</v>
-      </c>
+      <c r="E14" s="23"/>
       <c r="F14" s="23">
         <f>D14-E14</f>
         <v>0</v>
@@ -16107,10 +16106,7 @@
         <f>B15*C15</f>
         <v>0</v>
       </c>
-      <c r="E15" s="23">
-        <f t="shared" ref="E15:E17" si="0">B15-D15</f>
-        <v>0</v>
-      </c>
+      <c r="E15" s="23"/>
       <c r="F15" s="23">
         <f t="shared" ref="F15:F17" si="1">D15-E15</f>
         <v>0</v>
@@ -16126,10 +16122,7 @@
         <f t="shared" ref="D16:D17" si="2">B16*C16</f>
         <v>0</v>
       </c>
-      <c r="E16" s="23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="E16" s="23"/>
       <c r="F16" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16145,10 +16138,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E17" s="23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="E17" s="23"/>
       <c r="F17" s="23">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -16229,8 +16219,10 @@
       <c r="D21" s="18" t="s">
         <v>548</v>
       </c>
-      <c r="E21" s="18" t="s">
-        <v>549</v>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
       </c>
       <c r="F21" s="18" t="s">
         <v>550</v>
@@ -16248,10 +16240,7 @@
         <f>B22*C22</f>
         <v>0</v>
       </c>
-      <c r="E22" s="37">
-        <f>B22-D22</f>
-        <v>0</v>
-      </c>
+      <c r="E22" s="37"/>
       <c r="F22" s="37">
         <f>D22-E22</f>
         <v>0</v>
@@ -16269,10 +16258,7 @@
         <f>B23*C23</f>
         <v>0</v>
       </c>
-      <c r="E23" s="37">
-        <f>B23-D23</f>
-        <v>0</v>
-      </c>
+      <c r="E23" s="37"/>
       <c r="F23" s="37">
         <f t="shared" ref="F23:F24" si="3">D23-E23</f>
         <v>0</v>
@@ -16290,10 +16276,7 @@
         <f>B24*C24</f>
         <v>0</v>
       </c>
-      <c r="E24" s="37">
-        <f>B24-D24</f>
-        <v>0</v>
-      </c>
+      <c r="E24" s="37"/>
       <c r="F24" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -17897,15 +17880,15 @@
         <v>126</v>
       </c>
       <c r="B8" s="543">
-        <f>'原值明细表（按类别）D1-2'!B14</f>
+        <f>'原值明细表（按类别）D1-2'!B11</f>
         <v>0</v>
       </c>
       <c r="C8" s="543">
-        <f>'原值明细表（按类别）D1-2'!C14</f>
+        <f>'原值明细表（按类别）D1-2'!C11</f>
         <v>0</v>
       </c>
       <c r="D8" s="543">
-        <f>'原值明细表（按类别）D1-2'!D14</f>
+        <f>'原值明细表（按类别）D1-2'!D11</f>
         <v>0</v>
       </c>
       <c r="E8" s="544">
